--- a/Overpotnital/O2 BP/BOL/Edited/CN Polyol 1.5bp O2_unchanged.xlsx
+++ b/Overpotnital/O2 BP/BOL/Edited/CN Polyol 1.5bp O2_unchanged.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\My Drive\KAIST MASc 2021\Laboratory Work\Protocol\overpotential calculation\For paper SI\Overpotnital\O2 BP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\My Drive\KAIST MASc 2021\Laboratory Work\Protocol\overpotential calculation\For paper SI\Overpotnital\O2 BP\BOL\Edited\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63280EC-A7D3-4A0E-8C24-BFC33991857A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7425BE-315C-4588-9872-8CEBCCF69914}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23595" windowHeight="11265" xr2:uid="{7CB94D35-52ED-4DEA-9579-CC247F80CA29}"/>
   </bookViews>
